--- a/output/pdf_financials_xlsx/NUR.xlsx
+++ b/output/pdf_financials_xlsx/NUR.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/NUR.xlsx
+++ b/output/pdf_financials_xlsx/NUR.xlsx
@@ -2319,7 +2319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Director Director total</t>
+          <t>Director                                                                Director total</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director                                                                Director</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3897,673 +3897,711 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B a la n c e a s a t J a n u a r y 1 , 2 0</t>
+          <t>Net loss and total comprehensive income</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>5e-06</v>
+        <v>-8.75586</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>2e-06</v>
+        <v>-21.436048</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B a la n c e a s a t D e c e m b e r 3 1 , 2 0</t>
+          <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.084979</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.170246</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B a la n c e a s a t J a n u a ry 1 , 2 0</t>
+          <t>Depreciation of intangible assets</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.024245</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.050141</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>n g e s</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>n g e s</t>
+          <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.210269</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.185644</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(N o te 1 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>(N o te 1 )</t>
+          <t>Amortization of OID</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.54479</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>9e-06</v>
+        <v>1.418401</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(N o te 1 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(N o te 1 ) total</t>
+          <t>Interest on lease liabilities</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.034225</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.050051</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Interest on overdue payables</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.032156</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.230848</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-- total</t>
+          <t>Gain on debt settlement</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>-0.146946</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>9e-06</v>
+        <v>6.874318</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>it y</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>it y</t>
+          <t>Impairement of inventory</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>8e-06</v>
+        <v>0.00493</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>8e-06</v>
+        <v>0.001339</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>,5 7 1 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>,5 7 1 )</t>
+          <t>Impairement of receivable</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>6e-06</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.044169</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Impairment of assets</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>7e-06</v>
+        <v>0.072357</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>- total</t>
+          <t>Waive of lease liabilities</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>8e-06</v>
+        <v>-0.07564800000000001</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>,1 0 6 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>,1 0 6 )</t>
+          <t>Write-off of assets</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>7e-06</v>
+        <v>0.022274</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>8e-06</v>
+        <v>0.044245</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9 8 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9 8 ) total</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>6e-06</v>
+          <t>Write-off of accounts receivable</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.047056</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4 8 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4 8 ) total</t>
+          <t>Write-off of inventory</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.173193</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>9e-06</v>
+        <v>0.495907</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>s total</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>2e-06</v>
+          <t>Write off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>9e-06</v>
+        <v>-0.567079</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>c o n ve rs io n o p tio n</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>0</v>
+          <t>Write off of deferred revenue</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>9e-06</v>
+        <v>-0.820695</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(1 ,1 4 8 ,3 1 1 )--</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>(1 ,1 4 8 ,3 1 1 )--</t>
+          <t>Loss on modification of contract (Note 3)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>9e-06</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0</v>
+        <v>0.299659</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(8 0 1 ,8 0 2 )</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>T ra n s la tio n re s e rve</t>
+          <t>Bad Debt expense</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>7e-06</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.206975</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>d e fic it</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>d e fic it</t>
+          <t>Interest expense on factoring agreement</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.899321</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.06264</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>)</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>)</t>
+          <t>Interest expense on loans</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.728207</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.592295</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>d e fic it</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(1 1 ,4 1 7 ,0 5 5 )</t>
+          <t>Interest expense on convertible debentures</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.484043</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>d e fic it</t>
+          <t>Non-cash flow adjustments</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(2 1 ,4 3 6 ,0 4 8 )</t>
+          <t>Accretion of convertible debentures</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
-        <v>9e-06</v>
+        <v>0.762097</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0</v>
+        <v>0.8298759999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(1 8 4 ,4 1 7 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>(1 8 4 ,4 1 7 )</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
-        <v>6e-06</v>
+        <v>-1.945851</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>4e-06</v>
+        <v>-0.48873</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>(1 8 4 ,4 1 7 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>(1 8 4 ,4 1 7 ) total</t>
+          <t>Accrued revenues</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>9e-06</v>
+        <v>-0.226207</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>3e-06</v>
+        <v>1.518036</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>(5 ,1 6 7 ,6 8 4 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>(5 ,1 6 7 ,6 8 4 )</t>
+          <t>Tax credits receivable</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.032181</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>(1 ,1 7 0 ,8 7 8 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(1 ,1 7 0 ,8 7 8 )</t>
+          <t>Work in progress</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>-0.294217</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.273038</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>(1 ,1 7 0 ,8 7 8 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(1 ,1 7 0 ,8 7 8 ) total</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>-0.460335</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0</v>
+        <v>-0.941286</v>
       </c>
     </row>
     <row r="89">
@@ -4574,20 +4612,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net loss and total comprehensive income</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
-        <v>-8.75586</v>
+        <v>-0.009538</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-21.436048</v>
+        <v>-0.00645</v>
       </c>
     </row>
     <row r="90">
@@ -4598,20 +4640,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment</t>
+          <t>Security deposits and deposits on purchase of goods</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>0.084979</v>
+        <v>-0.491502</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.170246</v>
+        <v>0.003857</v>
       </c>
     </row>
     <row r="91">
@@ -4622,20 +4664,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Depreciation of intangible assets</t>
+          <t>Loan receivable</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>0.024245</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.050141</v>
+        <v>-0.077347</v>
       </c>
     </row>
     <row r="92">
@@ -4646,20 +4690,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
-        <v>0.210269</v>
+        <v>1.041313</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.185644</v>
+        <v>9.280094999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4670,20 +4718,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Amortization of OID</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
-        <v>0.54479</v>
+        <v>1.034425</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>1.418401</v>
+        <v>-1.366688</v>
       </c>
     </row>
     <row r="94">
@@ -4694,20 +4746,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
-        <v>0.034225</v>
+        <v>-6.221099</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.050051</v>
+        <v>-2.958887</v>
       </c>
     </row>
     <row r="95">
@@ -4718,20 +4774,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Interest on overdue payables</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Purchase of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
-        <v>0.032156</v>
+        <v>-0.035775</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.230848</v>
+        <v>-3.035744</v>
       </c>
     </row>
     <row r="96">
@@ -4742,20 +4802,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
+          <t>Purchase of intangible assets</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
-        <v>-0.146946</v>
+        <v>-0.357431</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>6.874318</v>
+        <v>-0.234079</v>
       </c>
     </row>
     <row r="97">
@@ -4766,20 +4826,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Impairement of inventory</t>
+          <t>Net cash generated in investing activities</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" s="5" t="n">
-        <v>0.00493</v>
+        <v>-0.393206</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.001339</v>
+        <v>-3.269824</v>
       </c>
     </row>
     <row r="98">
@@ -4790,22 +4850,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Impairement of receivable</t>
+          <t>Proceeds (repayment of) loan payable</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" s="5" t="n">
+        <v>3.829499</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.044169</v>
+        <v>4.778278</v>
       </c>
     </row>
     <row r="99">
@@ -4816,17 +4874,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Impairment of assets</t>
+          <t>Proceeds (repayment of) promissory notes</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" s="5" t="n">
-        <v>0.072357</v>
+        <v>0.63</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4842,22 +4900,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waive of lease liabilities</t>
+          <t>Proceeds (repayment of) from factoring agreement</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>-0.07564800000000001</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.255002</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-0.6971349999999999</v>
       </c>
     </row>
     <row r="101">
@@ -4868,20 +4924,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Write-off of assets</t>
+          <t>Repayment of loan payable</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" s="5" t="n">
-        <v>0.022274</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0.044245</v>
+        <v>-0.8094209999999999</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -4892,26 +4950,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Write-off of accounts receivable</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repayment of lease liabilities</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>-0.229529</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.047056</v>
+        <v>-0.257623</v>
       </c>
     </row>
     <row r="103">
@@ -4922,20 +4974,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Write-off of inventory</t>
+          <t>Convertible debenture and derivative liabilitiey</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="n">
-        <v>0.173193</v>
+        <v>3.008309</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.495907</v>
+        <v>6.112507</v>
       </c>
     </row>
     <row r="104">
@@ -4946,26 +4998,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Write off of accounts payable</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash generated in financing activities</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>7.683861</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.567079</v>
+        <v>9.936025000000001</v>
       </c>
     </row>
     <row r="105">
@@ -4976,26 +5022,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Write off of deferred revenue</t>
+          <t>Net increase in cash</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>1.069556</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-0.820695</v>
+        <v>3.707314</v>
       </c>
     </row>
     <row r="106">
@@ -5006,22 +5050,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Loss on modification of contract (Note 3)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.17288</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.299659</v>
+        <v>1.171558</v>
       </c>
     </row>
     <row r="107">
@@ -5032,22 +5078,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bad Debt expense</t>
+          <t>Foreign exchange in translation of foreign operations</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="5" t="n">
+        <v>-0.070878</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.206975</v>
+        <v>-0.213479</v>
       </c>
     </row>
     <row r="108">
@@ -5058,739 +5102,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non-cash flow adjustments</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Interest expense on factoring agreement</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
-        <v>0.899321</v>
+        <v>1.171558</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.06264</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Non-cash flow adjustments</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Interest expense on loans</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>0.728207</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.592295</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Non-cash flow adjustments</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Interest expense on convertible debentures</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" s="5" t="n">
-        <v>0.484043</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Non-cash flow adjustments</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Accretion of convertible debentures</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>0.762097</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0.8298759999999999</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Trade and other receivables</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>-1.945851</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>-0.48873</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Accrued revenues</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>-0.226207</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>1.518036</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Tax credits receivable</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" s="5" t="n">
-        <v>0.032181</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0.06660000000000001</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Work in progress</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>-0.294217</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0.273038</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ChangeInInventory</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>-0.460335</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-0.941286</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>-0.009538</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.00645</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Security deposits and deposits on purchase of goods</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="n">
-        <v>-0.491502</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.003857</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Loan receivable</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>-0.077347</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Trade and other payables</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>1.041313</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>9.280094999999999</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>1.034425</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>-1.366688</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Net change in working capital items</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>-6.221099</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>-2.958887</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Purchase of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>-0.035775</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>-3.035744</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Purchase of intangible assets</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" s="5" t="n">
-        <v>-0.357431</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>-0.234079</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Net cash generated in investing activities</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>-0.393206</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>-3.269824</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Proceeds (repayment of) loan payable</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" s="5" t="n">
-        <v>3.829499</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>4.778278</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Proceeds (repayment of) promissory notes</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Proceeds (repayment of) from factoring agreement</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="n">
-        <v>1.255002</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>-0.6971349999999999</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Repayment of loan payable</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>-0.8094209999999999</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Repayment of lease liabilities</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" s="5" t="n">
-        <v>-0.229529</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>-0.257623</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Convertible debenture and derivative liabilitiey</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>3.008309</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>6.112507</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Net cash generated in financing activities</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>7.683861</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>9.936025000000001</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Net increase in cash</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>1.069556</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>3.707314</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0.17288</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>1.171558</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Foreign exchange in translation of foreign operations</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>-0.070878</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>-0.213479</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>1.171558</v>
-      </c>
-      <c r="F136" s="5" t="n">
         <v>4.665392</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/NUR.xlsx
+++ b/output/pdf_financials_xlsx/NUR.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.171558</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.665392</v>
       </c>
     </row>
     <row r="35">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.171558</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.665392</v>
       </c>
     </row>
     <row r="37">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.900243</v>
+        <v>5.728685</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.812034000000001</v>
+        <v>4.146642</v>
       </c>
     </row>
     <row r="49">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NUR.xlsx
+++ b/output/pdf_financials_xlsx/NUR.xlsx
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.295248</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.35589</v>
       </c>
     </row>
     <row r="101">
@@ -3934,7 +3934,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>0.084979</v>
       </c>
@@ -3982,7 +3986,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.210269</v>
       </c>

--- a/output/pdf_financials_xlsx/NUR.xlsx
+++ b/output/pdf_financials_xlsx/NUR.xlsx
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.357431</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.234079</v>
       </c>
     </row>
     <row r="117">
@@ -4818,7 +4818,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>-0.357431</v>
       </c>
